--- a/testdata/fixtures/payments_valid.xlsx
+++ b/testdata/fixtures/payments_valid.xlsx
@@ -100,9 +100,6 @@
     <t xml:space="preserve">Détendeur et gilet</t>
   </si>
   <si>
-    <t xml:space="preserve">Commentaire privé du paiement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mme</t>
   </si>
   <si>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t xml:space="preserve">10/05/2026 09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plongée offerte par le club, accord du bureau</t>
   </si>
   <si>
     <t xml:space="preserve">01/05/2026 12:00:00</t>
@@ -384,23 +384,20 @@
       <c r="P2">
         <v>46027.4375</v>
       </c>
-      <c r="Q2" t="s">
-        <v>30</v>
-      </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" t="s">
         <v>34</v>
-      </c>
-      <c r="X2" t="s">
-        <v>35</v>
       </c>
       <c r="Y2">
         <v>0</v>
@@ -423,7 +420,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
         <v>27</v>
@@ -434,23 +431,20 @@
       <c r="O3" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" t="s">
-        <v>30</v>
-      </c>
       <c r="R3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" t="s">
         <v>34</v>
-      </c>
-      <c r="X3" t="s">
-        <v>35</v>
       </c>
       <c r="Y3">
         <v>0</v>
@@ -473,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
         <v>27</v>
@@ -484,23 +478,20 @@
       <c r="O4" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" t="s">
-        <v>30</v>
-      </c>
       <c r="R4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y4">
         <v>0</v>
@@ -523,34 +514,31 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
         <v>38</v>
       </c>
-      <c r="I5" t="s">
+      <c r="O5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" t="s">
+        <v>30</v>
+      </c>
+      <c r="S5" t="s">
+        <v>31</v>
+      </c>
+      <c r="T5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" t="s">
         <v>39</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>30</v>
-      </c>
-      <c r="R5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" t="s">
-        <v>32</v>
-      </c>
-      <c r="T5" t="s">
-        <v>33</v>
-      </c>
-      <c r="U5" t="s">
-        <v>34</v>
-      </c>
-      <c r="X5" t="s">
-        <v>40</v>
       </c>
       <c r="Y5">
         <v>0</v>
@@ -576,31 +564,31 @@
         <v>25</v>
       </c>
       <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
         <v>41</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>42</v>
       </c>
-      <c r="J6" t="s">
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" t="s">
         <v>43</v>
       </c>
-      <c r="O6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>30</v>
-      </c>
       <c r="R6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X6" t="s">
         <v>44</v>
@@ -640,20 +628,17 @@
       <c r="O7" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" t="s">
-        <v>30</v>
-      </c>
       <c r="R7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X7" t="s">
         <v>46</v>
@@ -679,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
         <v>47</v>
@@ -687,20 +672,17 @@
       <c r="O8" t="s">
         <v>29</v>
       </c>
-      <c r="Q8" t="s">
-        <v>30</v>
-      </c>
       <c r="R8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X8" t="s">
         <v>48</v>
@@ -729,7 +711,7 @@
         <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I9" t="s">
         <v>50</v>
@@ -737,20 +719,17 @@
       <c r="O9" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" t="s">
-        <v>30</v>
-      </c>
       <c r="R9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X9" t="s">
         <v>51</v>
@@ -787,20 +766,17 @@
       <c r="O10" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" t="s">
-        <v>30</v>
-      </c>
       <c r="R10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X10" t="s">
         <v>52</v>
@@ -829,7 +805,7 @@
         <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
         <v>54</v>
@@ -837,20 +813,17 @@
       <c r="O11" t="s">
         <v>29</v>
       </c>
-      <c r="Q11" t="s">
-        <v>30</v>
-      </c>
       <c r="R11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X11" t="s">
         <v>55</v>
@@ -879,7 +852,7 @@
         <v>56</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>54</v>
@@ -890,20 +863,17 @@
       <c r="O12" t="s">
         <v>29</v>
       </c>
-      <c r="Q12" t="s">
-        <v>30</v>
-      </c>
       <c r="R12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X12" t="s">
         <v>57</v>
@@ -932,7 +902,7 @@
         <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s">
         <v>58</v>
@@ -940,20 +910,17 @@
       <c r="O13" t="s">
         <v>59</v>
       </c>
-      <c r="Q13" t="s">
-        <v>30</v>
-      </c>
       <c r="R13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -985,31 +952,28 @@
         <v>25</v>
       </c>
       <c r="G14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
         <v>41</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>42</v>
       </c>
-      <c r="J14" t="s">
-        <v>43</v>
-      </c>
       <c r="O14" t="s">
         <v>29</v>
       </c>
-      <c r="Q14" t="s">
-        <v>30</v>
-      </c>
       <c r="R14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X14" t="s">
         <v>63</v>
@@ -1038,31 +1002,28 @@
         <v>25</v>
       </c>
       <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
         <v>41</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>42</v>
       </c>
-      <c r="J15" t="s">
-        <v>43</v>
-      </c>
       <c r="O15" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" t="s">
-        <v>30</v>
-      </c>
       <c r="R15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X15" t="s">
         <v>63</v>
@@ -1091,31 +1052,28 @@
         <v>25</v>
       </c>
       <c r="G16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" t="s">
         <v>41</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>42</v>
       </c>
-      <c r="J16" t="s">
-        <v>43</v>
-      </c>
       <c r="O16" t="s">
         <v>29</v>
       </c>
-      <c r="Q16" t="s">
-        <v>30</v>
-      </c>
       <c r="R16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X16" t="s">
         <v>66</v>
@@ -1141,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" t="s">
         <v>27</v>
@@ -1152,20 +1110,17 @@
       <c r="O17" t="s">
         <v>29</v>
       </c>
-      <c r="Q17" t="s">
-        <v>30</v>
-      </c>
       <c r="R17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X17" t="s">
         <v>69</v>
@@ -1194,7 +1149,7 @@
         <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I18" t="s">
         <v>54</v>
@@ -1202,20 +1157,17 @@
       <c r="O18" t="s">
         <v>29</v>
       </c>
-      <c r="Q18" t="s">
-        <v>30</v>
-      </c>
       <c r="R18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X18" t="s">
         <v>72</v>
@@ -1252,20 +1204,17 @@
       <c r="O19" t="s">
         <v>29</v>
       </c>
-      <c r="Q19" t="s">
-        <v>30</v>
-      </c>
       <c r="R19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X19" t="s">
         <v>76</v>
@@ -1302,20 +1251,17 @@
       <c r="O20" t="s">
         <v>29</v>
       </c>
-      <c r="Q20" t="s">
-        <v>30</v>
-      </c>
       <c r="R20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X20">
         <v>46174.5</v>
@@ -1352,20 +1298,17 @@
       <c r="O21" t="s">
         <v>29</v>
       </c>
-      <c r="Q21" t="s">
-        <v>30</v>
-      </c>
       <c r="R21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X21" t="s">
         <v>83</v>
@@ -1402,20 +1345,17 @@
       <c r="O22" t="s">
         <v>29</v>
       </c>
-      <c r="Q22" t="s">
-        <v>30</v>
-      </c>
       <c r="R22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X22" t="s">
         <v>85</v>
